--- a/config/validation_rulebook.xlsx
+++ b/config/validation_rulebook.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="bs_checks" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="is_checks" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="cf_checks" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bs_checks" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="is_checks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cf_checks" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +523,6 @@
           <t>error</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>BS010+BS011+BS012</t>
@@ -571,7 +570,6 @@
           <t>error</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>BS001+BS002+BS003+BS004+BS007+BS008+BS009+BS013+BS014+BS016+BS017+BS018+BS019+BS020+BS021</t>
@@ -619,7 +617,6 @@
           <t>error</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>BS041+BS043</t>
@@ -667,7 +664,6 @@
           <t>error</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>BS045+BS046</t>
@@ -715,7 +711,6 @@
           <t>error</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>BS029+BS030+BS031+BS032+BS033+BS034+BS035+BS036+BS037+BS038+BS039+BS040+BS041+BS044+BS047+BS048+BS049+BS050+BS051+BS052+BS053+BS054+BS055</t>
@@ -763,7 +758,6 @@
           <t>error</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>BS103+BS120</t>
@@ -811,7 +805,6 @@
           <t>error</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>BS27+BS56</t>
@@ -859,7 +852,6 @@
           <t>error</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>BS063+BS064</t>
@@ -907,7 +899,6 @@
           <t>error</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>BS071+BS072+BS073</t>
@@ -937,7 +928,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BS059,BS060,BS061,BS062,BS065,BS066,BS067,BS068,BS069,BS070,BS074,BS075,BS0706,BS077,BS078,BS079,BS080</t>
+          <t>BS059,BS060,BS061,BS062,BS065,BS066,BS067,BS068,BS069,BS070,BS074,BS075,BS076,BS077,BS078,BS079,BS080</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -962,7 +953,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>BS059+BS060+BS061+BS062+BS065+BS066+BS067+BS068+BS069+BS070+BS074+BS075+BS0706+BS077+BS078+BS079+BS080</t>
+          <t>BS059+BS060+BS061+BS062+BS065+BS066+BS067+BS068+BS069+BS070+BS074+BS075+BS076+BS077+BS078+BS079+BS080</t>
         </is>
       </c>
     </row>
@@ -1007,7 +998,6 @@
           <t>error</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>BS095+BS096</t>
@@ -1107,7 +1097,6 @@
           <t>error</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>BS089+BS102</t>
@@ -1145,17 +1134,19 @@
           <t>0.05</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G15" t="n">
+        <v>0</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>????DEBT999????????????????????</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>BS059+BS075+BS078+BS091+BS092+BS093+BS095</t>
@@ -1203,7 +1194,6 @@
           <t>error</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>BS005+BS006</t>
